--- a/regressao_simples_por_municipio.xlsx
+++ b/regressao_simples_por_municipio.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="valor_agropecuaria" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="empilhado" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,6 +920,1356 @@
         <v>12</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Aquidauana</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>pib_per_capita</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.06803007493178069</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1694.301731416889</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9793449648968661</v>
+      </c>
+      <c r="F17" t="n">
+        <v>9.332583594573394e-10</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.003124252101345406</v>
+      </c>
+      <c r="H17" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Barão de Melgaço</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>pib_per_capita</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.04565891038140009</v>
+      </c>
+      <c r="D18" t="n">
+        <v>622.4450366780192</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7692773911801217</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.0001791316171150237</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.007907316741355712</v>
+      </c>
+      <c r="H18" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Corumbá</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>pib_per_capita</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.1493018049316192</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2127.428687051181</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.5954051489596386</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.003285655124479269</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.03891965131848291</v>
+      </c>
+      <c r="H19" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Coxim</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>pib_per_capita</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.005717940082364915</v>
+      </c>
+      <c r="D20" t="n">
+        <v>890.3270455826266</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9437946405160161</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.413894398453612e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.0004412550732566128</v>
+      </c>
+      <c r="H20" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>pib_per_capita</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.02814996000098598</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2872.753358843627</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9710581381556502</v>
+      </c>
+      <c r="F21" t="n">
+        <v>5.058679207098941e-09</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.001536803705334175</v>
+      </c>
+      <c r="H21" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Itiquira</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>pib_per_capita</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.001411828480470503</v>
+      </c>
+      <c r="D22" t="n">
+        <v>172.6182226711216</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.5440288005184423</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.006182953990909164</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.0004087329962162269</v>
+      </c>
+      <c r="H22" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ladário</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>pib_per_capita</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.000424672768985123</v>
+      </c>
+      <c r="D23" t="n">
+        <v>114.5333407175474</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.6454317724094574</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.001645971770495925</v>
+      </c>
+      <c r="G23" t="n">
+        <v>9.953576345355962e-05</v>
+      </c>
+      <c r="H23" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Miranda</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>pib_per_capita</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.002049711739386137</v>
+      </c>
+      <c r="D24" t="n">
+        <v>176.957913083188</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.8973594234909655</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.931921068521286e-06</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.0002192144185397599</v>
+      </c>
+      <c r="H24" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Nossa Senhora do Livramento</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>pib_per_capita</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.005657831232973341</v>
+      </c>
+      <c r="D25" t="n">
+        <v>178.1098353764087</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.974640895518004</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.608617328663893e-09</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.0002885988725782909</v>
+      </c>
+      <c r="H25" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Poconé</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>pib_per_capita</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.02521273045319243</v>
+      </c>
+      <c r="D26" t="n">
+        <v>739.885895487126</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9747624991955516</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.546537282363869e-09</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.001282902487906435</v>
+      </c>
+      <c r="H26" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Porto Esperidião</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>pib_per_capita</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.004389366874888435</v>
+      </c>
+      <c r="D27" t="n">
+        <v>466.1758106269728</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8304695921062039</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.719926878406466e-05</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.0006271390123111231</v>
+      </c>
+      <c r="H27" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Porto Murtinho</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>pib_per_capita</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.02769500370549342</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2964.697523163562</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8941079443213039</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.431791813990392e-06</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.00301396455373313</v>
+      </c>
+      <c r="H28" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Rio Verde de Mato Grosso</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>pib_per_capita</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.02882934410429443</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1986.500313820454</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9741184756510992</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.889260872886687e-09</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.00148601706706229</v>
+      </c>
+      <c r="H29" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Santo Antônio do Leverger</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>pib_per_capita</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.01266529797555285</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1773.258587046369</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.722826508127755</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.0004595059876402214</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.002480128728085178</v>
+      </c>
+      <c r="H30" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>pib_per_capita</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.00298472829159681</v>
+      </c>
+      <c r="D31" t="n">
+        <v>392.2129531510975</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7864254411165864</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.0001206751083178127</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.00049187050841753</v>
+      </c>
+      <c r="H31" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Aquidauana</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>valor_industria</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.015853499366388</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1760.713126859672</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.7932909225214959</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.0001021282540449282</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.002559108336725688</v>
+      </c>
+      <c r="H32" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Barão de Melgaço</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>valor_industria</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.1394984563038664</v>
+      </c>
+      <c r="D33" t="n">
+        <v>822.0709056351764</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.942270608101236</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.617347746188252e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.01091892972503594</v>
+      </c>
+      <c r="H33" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Corumbá</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>valor_industria</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>-4.376337116539057e-05</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5928.035998423016</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.000113927896992827</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.9737366781863281</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.001296495423587942</v>
+      </c>
+      <c r="H34" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Coxim</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>valor_industria</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.0008014670143171882</v>
+      </c>
+      <c r="D35" t="n">
+        <v>973.1450668374554</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.1286066885529978</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.2523271489584144</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.000659722029109545</v>
+      </c>
+      <c r="H35" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>valor_industria</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.002687590487471766</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3011.035303299032</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8162953401378387</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5.596673096126406e-05</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.0004031805036175055</v>
+      </c>
+      <c r="H36" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Itiquira</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>valor_industria</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.0004446826226037483</v>
+      </c>
+      <c r="D37" t="n">
+        <v>189.3612658179989</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8860607537098675</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.967995811510835e-06</v>
+      </c>
+      <c r="G37" t="n">
+        <v>5.042606497495777e-05</v>
+      </c>
+      <c r="H37" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ladário</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>valor_industria</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.0001858497645842875</v>
+      </c>
+      <c r="D38" t="n">
+        <v>115.8838260906112</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.2818615460344194</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.07572969539516083</v>
+      </c>
+      <c r="G38" t="n">
+        <v>9.380979602149046e-05</v>
+      </c>
+      <c r="H38" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Miranda</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>valor_industria</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.0006099569107954647</v>
+      </c>
+      <c r="D39" t="n">
+        <v>192.7911785273474</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.5593581912006149</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.005156404807612144</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.0001711973373467971</v>
+      </c>
+      <c r="H39" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Nossa Senhora do Livramento</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>valor_industria</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.0009838877125015228</v>
+      </c>
+      <c r="D40" t="n">
+        <v>238.4058062201069</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7355180696848204</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.0003609954459453855</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.0001865721715793</v>
+      </c>
+      <c r="H40" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Poconé</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>valor_industria</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.007877664315881055</v>
+      </c>
+      <c r="D41" t="n">
+        <v>802.0638855648713</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.8083577779386157</v>
+      </c>
+      <c r="F41" t="n">
+        <v>6.942295300106512e-05</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.001212945419654063</v>
+      </c>
+      <c r="H41" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Porto Esperidião</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>valor_industria</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.0009682571787064608</v>
+      </c>
+      <c r="D42" t="n">
+        <v>518.1282583340389</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.462498821484442</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.01495446421685382</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.0003300844919378394</v>
+      </c>
+      <c r="H42" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Porto Murtinho</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>valor_industria</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.01027556917203292</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3635.183037591218</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.2136316274394234</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.1303217251892414</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.006234277528623896</v>
+      </c>
+      <c r="H43" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Rio Verde de Mato Grosso</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>valor_industria</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.01642769034276627</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2160.581847930466</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.7377811775338182</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.0003453891728616121</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.003097024590811641</v>
+      </c>
+      <c r="H44" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Santo Antônio do Leverger</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>valor_industria</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.01000853021014117</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1784.603377282958</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.8093959880297054</v>
+      </c>
+      <c r="F45" t="n">
+        <v>6.752766839274716e-05</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.001535874746451893</v>
+      </c>
+      <c r="H45" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>valor_industria</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.0005864478447126199</v>
+      </c>
+      <c r="D46" t="n">
+        <v>438.6224742158246</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.8448240247614477</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2.373516869201165e-05</v>
+      </c>
+      <c r="G46" t="n">
+        <v>7.948011895669084e-05</v>
+      </c>
+      <c r="H46" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Aquidauana</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>valor_administracao_publica</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.004447528403917653</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1817.584156908023</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9658083130842879</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.166767321656191e-08</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.0002646266170140546</v>
+      </c>
+      <c r="H47" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Barão de Melgaço</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>valor_administracao_publica</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.009781941442053164</v>
+      </c>
+      <c r="D48" t="n">
+        <v>714.8213167491601</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.9639845003998627</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.514151247686831e-08</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.0005979085377715952</v>
+      </c>
+      <c r="H48" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Corumbá</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>valor_administracao_publica</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.00442296441534855</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3012.577471880915</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.9645196806523071</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.404622721431889e-08</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.0002682573675791384</v>
+      </c>
+      <c r="H49" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Coxim</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>valor_administracao_publica</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.0006380978686251503</v>
+      </c>
+      <c r="D50" t="n">
+        <v>918.3904039900306</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.9866374571417623</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.054334275609303e-10</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2.348297144322712e-05</v>
+      </c>
+      <c r="H50" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>valor_administracao_publica</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.0009643119598314429</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2938.774441865108</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.9930847925927317</v>
+      </c>
+      <c r="F51" t="n">
+        <v>3.902849102456292e-12</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2.54464376675252e-05</v>
+      </c>
+      <c r="H51" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Itiquira</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>valor_administracao_publica</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.001876537701170543</v>
+      </c>
+      <c r="D52" t="n">
+        <v>145.2401323230675</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.9509563018205656</v>
+      </c>
+      <c r="F52" t="n">
+        <v>7.129945907136014e-08</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.0001347623635501878</v>
+      </c>
+      <c r="H52" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Ladário</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>valor_administracao_publica</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>4.344420839497311e-05</v>
+      </c>
+      <c r="D53" t="n">
+        <v>114.7571547700349</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.9608444964726324</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2.302891700852993e-08</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2.773331225036911e-06</v>
+      </c>
+      <c r="H53" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Miranda</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>valor_administracao_publica</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.0002050362000475162</v>
+      </c>
+      <c r="D54" t="n">
+        <v>181.1005480647655</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.9470906962282456</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.043668047093246e-07</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1.532501056662663e-05</v>
+      </c>
+      <c r="H54" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Nossa Senhora do Livramento</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>valor_administracao_publica</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.002228886671270371</v>
+      </c>
+      <c r="D55" t="n">
+        <v>134.8935944895242</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.9720072018619375</v>
+      </c>
+      <c r="F55" t="n">
+        <v>4.28016264958955e-09</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.0001196124543826085</v>
+      </c>
+      <c r="H55" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Poconé</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>valor_administracao_publica</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.002408260522491466</v>
+      </c>
+      <c r="D56" t="n">
+        <v>729.9675403732015</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.9784320325627727</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.159008410272341e-09</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.000113068790069827</v>
+      </c>
+      <c r="H56" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Porto Esperidião</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>valor_administracao_publica</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.001111667598901664</v>
+      </c>
+      <c r="D57" t="n">
+        <v>470.5839108955809</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.9689173971511079</v>
+      </c>
+      <c r="F57" t="n">
+        <v>7.234182630199534e-09</v>
+      </c>
+      <c r="G57" t="n">
+        <v>6.296370282662665e-05</v>
+      </c>
+      <c r="H57" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Porto Murtinho</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>valor_administracao_publica</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.003981095333917752</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3106.986747206744</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.9481708540436811</v>
+      </c>
+      <c r="F58" t="n">
+        <v>9.409523315867584e-08</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.0002943379787590304</v>
+      </c>
+      <c r="H58" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Rio Verde de Mato Grosso</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>valor_administracao_publica</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.005214392614385881</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2031.946030120472</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.9833289958590852</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3.191157006629944e-10</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.0002147015525352123</v>
+      </c>
+      <c r="H59" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Santo Antônio do Leverger</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>valor_administracao_publica</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.006096835240615573</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1532.603249128626</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.9560616760049494</v>
+      </c>
+      <c r="F60" t="n">
+        <v>4.106055540832617e-08</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.0004133169800725263</v>
+      </c>
+      <c r="H60" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>valor_administracao_publica</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.0007652629942245296</v>
+      </c>
+      <c r="D61" t="n">
+        <v>420.7823080888001</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.9245795043744012</v>
+      </c>
+      <c r="F61" t="n">
+        <v>6.203884985359474e-07</v>
+      </c>
+      <c r="G61" t="n">
+        <v>6.911674428854083e-05</v>
+      </c>
+      <c r="H61" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
